--- a/workspaces/yzz100497/output/影展投稿整理结果.xlsx
+++ b/workspaces/yzz100497/output/影展投稿整理结果.xlsx
@@ -510,7 +510,7 @@
         <v>待补材料</v>
       </c>
       <c r="R2" t="str">
-        <v>[信息] 发现作者名多种写法: 张 三、张三; [提醒] 发现跨作品重复投稿图片: DSC0001.jpg (城市夜景)、DSC0001_copy.jpg (张 三); [提醒] 作品 "未命名作品" 缺少作品说明</v>
+        <v>[信息] 发现作者名多种写法: 张 三、张三; [待补] 发现跨作品重复投稿图片: DSC0001.jpg (城市夜景)、DSC0001_copy.jpg (张 三); [待补] 作品 "未命名作品" 缺少作品说明</v>
       </c>
     </row>
     <row r="3">
@@ -566,7 +566,7 @@
         <v>待补材料</v>
       </c>
       <c r="R3" t="str">
-        <v>[信息] 发现作者名多种写法: 张 三、张三; [提醒] 发现跨作品重复投稿图片: DSC0001.jpg (城市夜景)、DSC0001_copy.jpg (张 三); [提醒] 作品 "未命名作品" 缺少作品说明</v>
+        <v>[信息] 发现作者名多种写法: 张 三、张三; [待补] 发现跨作品重复投稿图片: DSC0001.jpg (城市夜景)、DSC0001_copy.jpg (张 三); [待补] 作品 "未命名作品" 缺少作品说明</v>
       </c>
     </row>
     <row r="4">
@@ -622,7 +622,7 @@
         <v>待补材料</v>
       </c>
       <c r="R4" t="str">
-        <v>[信息] 发现作者名多种写法: 张 三、张三; [提醒] 发现跨作品重复投稿图片: DSC0001.jpg (城市夜景)、DSC0001_copy.jpg (张 三); [提醒] 作品 "未命名作品" 缺少作品说明</v>
+        <v>[信息] 发现作者名多种写法: 张 三、张三; [待补] 发现跨作品重复投稿图片: DSC0001.jpg (城市夜景)、DSC0001_copy.jpg (张 三); [待补] 作品 "未命名作品" 缺少作品说明</v>
       </c>
     </row>
     <row r="5">
@@ -678,7 +678,7 @@
         <v>待补材料</v>
       </c>
       <c r="R5" t="str">
-        <v>[信息] 发现作者名多种写法: 张 三、张三; [提醒] 发现跨作品重复投稿图片: DSC0001.jpg (城市夜景)、DSC0001_copy.jpg (张 三); [提醒] 作品 "未命名作品" 缺少作品说明</v>
+        <v>[信息] 发现作者名多种写法: 张 三、张三; [待补] 发现跨作品重复投稿图片: DSC0001.jpg (城市夜景)、DSC0001_copy.jpg (张 三); [待补] 作品 "未命名作品" 缺少作品说明</v>
       </c>
     </row>
     <row r="6">
@@ -734,7 +734,7 @@
         <v>待补材料</v>
       </c>
       <c r="R6" t="str">
-        <v>[信息] 发现作者名多种写法: 张 三、张三; [提醒] 发现跨作品重复投稿图片: DSC0001.jpg (城市夜景)、DSC0001_copy.jpg (张 三); [提醒] 作品 "未命名作品" 缺少作品说明</v>
+        <v>[信息] 发现作者名多种写法: 张 三、张三; [待补] 发现跨作品重复投稿图片: DSC0001.jpg (城市夜景)、DSC0001_copy.jpg (张 三); [待补] 作品 "未命名作品" 缺少作品说明</v>
       </c>
     </row>
   </sheetData>
@@ -857,7 +857,7 @@
         <v>退回</v>
       </c>
       <c r="R2" t="str">
-        <v>[退回] 授权书缺少签字; [提醒] 作品 "老街记忆" 缺少作品说明; [退回] 图片尺寸过小: 800x600 (0.48MP)，最低要求 2MP</v>
+        <v>[退回] 授权书缺少签字; [待补] 作品 "老街记忆" 缺少作品说明; [退回] 图片尺寸过小: 800x600 (0.48MP)，最低要求 2MP</v>
       </c>
     </row>
     <row r="3">
@@ -1025,7 +1025,7 @@
         <v>退回</v>
       </c>
       <c r="R5" t="str">
-        <v>[提醒] 缺少作者简介; [退回] 缺少授权书; [提醒] 作品 "small_photo" 缺少作品说明; [退回] 图片尺寸过小: 640x480 (0.31MP)，最低要求 2MP</v>
+        <v>[待补] 缺少作者简介; [退回] 缺少授权书; [待补] 作品 "small_photo" 缺少作品说明; [退回] 图片尺寸过小: 640x480 (0.31MP)，最低要求 2MP</v>
       </c>
     </row>
   </sheetData>
@@ -1037,7 +1037,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1058,67 +1058,67 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>作者名不一致</v>
+        <v>压缩包</v>
       </c>
       <c r="B2" t="str">
-        <v>信息</v>
+        <v>警告</v>
       </c>
       <c r="C2" t="str">
-        <v>发现作者名多种写法: 张 三、张三</v>
+        <v>发现压缩包: 压缩包投稿.zip，请手动检查内容</v>
       </c>
       <c r="D2" t="str">
-        <v>51548ffb97ff80f7</v>
+        <v>c998dcae6522f16f</v>
       </c>
       <c r="E2" t="str">
-        <v>author</v>
+        <v>document</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>重复投稿</v>
+        <v>网盘链接</v>
       </c>
       <c r="B3" t="str">
         <v>警告</v>
       </c>
       <c r="C3" t="str">
-        <v>发现跨作品重复投稿图片: DSC0001.jpg (城市夜景)、DSC0001_copy.jpg (张 三)</v>
+        <v>发现网盘链接 (百度网盘): https://pan.baidu.com/s/1abcdefghijklmnopqr，请手动下载检查</v>
       </c>
       <c r="D3" t="str">
-        <v>51548ffb97ff80f7</v>
+        <v>27db01b39f8bbcae</v>
       </c>
       <c r="E3" t="str">
-        <v>author</v>
+        <v>document</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>缺少签字</v>
+        <v>作者名不一致</v>
       </c>
       <c r="B4" t="str">
-        <v>错误</v>
+        <v>信息</v>
       </c>
       <c r="C4" t="str">
-        <v>授权书缺少签字</v>
+        <v>发现作者名多种写法: 张 三、张三</v>
       </c>
       <c r="D4" t="str">
-        <v>87cb07dfca0892a9</v>
+        <v>516599e97d8b5853</v>
       </c>
       <c r="E4" t="str">
-        <v>document</v>
+        <v>author</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>缺少授权书</v>
+        <v>重复投稿</v>
       </c>
       <c r="B5" t="str">
-        <v>错误</v>
+        <v>警告</v>
       </c>
       <c r="C5" t="str">
-        <v>缺少授权书</v>
+        <v>发现跨作品重复投稿图片: DSC0001.jpg (城市夜景)、DSC0001_copy.jpg (张 三)</v>
       </c>
       <c r="D5" t="str">
-        <v>4600d2807217f30b</v>
+        <v>516599e97d8b5853</v>
       </c>
       <c r="E5" t="str">
         <v>author</v>
@@ -1126,19 +1126,19 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>缺少文档</v>
+        <v>缺少签字</v>
       </c>
       <c r="B6" t="str">
-        <v>警告</v>
+        <v>错误</v>
       </c>
       <c r="C6" t="str">
-        <v>缺少作者简介</v>
+        <v>授权书缺少签字</v>
       </c>
       <c r="D6" t="str">
-        <v>aecbfaa1395cc1af</v>
+        <v>d5dccb2e1fc6a028</v>
       </c>
       <c r="E6" t="str">
-        <v>author</v>
+        <v>document</v>
       </c>
     </row>
     <row r="7">
@@ -1152,7 +1152,7 @@
         <v>缺少授权书</v>
       </c>
       <c r="D7" t="str">
-        <v>aecbfaa1395cc1af</v>
+        <v>e0c5d379c9e43f17</v>
       </c>
       <c r="E7" t="str">
         <v>author</v>
@@ -1166,30 +1166,30 @@
         <v>警告</v>
       </c>
       <c r="C8" t="str">
-        <v>作品 "未命名作品" 缺少作品说明</v>
+        <v>缺少作者简介</v>
       </c>
       <c r="D8" t="str">
-        <v>1b0e15fad66b7e03</v>
+        <v>889ed3c76dc2e107</v>
       </c>
       <c r="E8" t="str">
-        <v>work</v>
+        <v>author</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>缺少文档</v>
+        <v>缺少授权书</v>
       </c>
       <c r="B9" t="str">
-        <v>警告</v>
+        <v>错误</v>
       </c>
       <c r="C9" t="str">
-        <v>作品 "老街记忆" 缺少作品说明</v>
+        <v>缺少授权书</v>
       </c>
       <c r="D9" t="str">
-        <v>acf100e4d44ff776</v>
+        <v>889ed3c76dc2e107</v>
       </c>
       <c r="E9" t="str">
-        <v>work</v>
+        <v>author</v>
       </c>
     </row>
     <row r="10">
@@ -1200,10 +1200,10 @@
         <v>警告</v>
       </c>
       <c r="C10" t="str">
-        <v>作品 "small_photo" 缺少作品说明</v>
+        <v>作品 "未命名作品" 缺少作品说明</v>
       </c>
       <c r="D10" t="str">
-        <v>52f8d15bad2f4b56</v>
+        <v>6b4c95393295f191</v>
       </c>
       <c r="E10" t="str">
         <v>work</v>
@@ -1211,41 +1211,75 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>图片过小</v>
+        <v>缺少文档</v>
       </c>
       <c r="B11" t="str">
-        <v>错误</v>
+        <v>警告</v>
       </c>
       <c r="C11" t="str">
-        <v>图片尺寸过小: 800x600 (0.48MP)，最低要求 2MP</v>
+        <v>作品 "老街记忆" 缺少作品说明</v>
       </c>
       <c r="D11" t="str">
-        <v>c377dcffd54e1770</v>
+        <v>ed53e5ecffe85290</v>
       </c>
       <c r="E11" t="str">
-        <v>photo</v>
+        <v>work</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
+        <v>缺少文档</v>
+      </c>
+      <c r="B12" t="str">
+        <v>警告</v>
+      </c>
+      <c r="C12" t="str">
+        <v>作品 "small_photo" 缺少作品说明</v>
+      </c>
+      <c r="D12" t="str">
+        <v>1cc16c77b3919785</v>
+      </c>
+      <c r="E12" t="str">
+        <v>work</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
         <v>图片过小</v>
       </c>
-      <c r="B12" t="str">
+      <c r="B13" t="str">
         <v>错误</v>
       </c>
-      <c r="C12" t="str">
+      <c r="C13" t="str">
+        <v>图片尺寸过小: 800x600 (0.48MP)，最低要求 2MP</v>
+      </c>
+      <c r="D13" t="str">
+        <v>c7cc92b50735c3e3</v>
+      </c>
+      <c r="E13" t="str">
+        <v>photo</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>图片过小</v>
+      </c>
+      <c r="B14" t="str">
+        <v>错误</v>
+      </c>
+      <c r="C14" t="str">
         <v>图片尺寸过小: 640x480 (0.31MP)，最低要求 2MP</v>
       </c>
-      <c r="D12" t="str">
-        <v>7fe00e7c686e5b6a</v>
-      </c>
-      <c r="E12" t="str">
+      <c r="D14" t="str">
+        <v>f740d6a1f2c92838</v>
+      </c>
+      <c r="E14" t="str">
         <v>photo</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E14"/>
   </ignoredErrors>
 </worksheet>
 </file>